--- a/testFile/case/PatrolExcel.xlsx
+++ b/testFile/case/PatrolExcel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17475" windowHeight="8062" activeTab="2"/>
+    <workbookView windowWidth="20317" windowHeight="9727" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="patrol" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,25 @@
     <sheet name="device" sheetId="3" r:id="rId3"/>
     <sheet name="bus" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="472">
   <si>
     <t>测试用例编号</t>
   </si>
@@ -1908,6 +1921,106 @@
     <t>/buswash/device/outside_screen/config_info/1</t>
   </si>
   <si>
+    <t>设备管理模块/周界相机</t>
+  </si>
+  <si>
+    <t>周界相机增改</t>
+  </si>
+  <si>
+    <t>/buswash/device/perimeter/camera/cu</t>
+  </si>
+  <si>
+    <t>{
+  "id": 240616,
+  "stationNum": "10000662",
+  "enabled": 1,
+  "deviceName": "小房间摄像头-03石桥-利旧",
+  "bindDeviceId": "1ef588f355d94dbabf787a72897322d2",
+  "siteId": 6,
+  "siteName": "石桥公交停车场",
+  "corOrgName": "三公司",
+  "createTime": "2024-08-29 17:15:05",
+  "heartTime": "2024-10-12 17:08:15",
+  "operatorName": "管理员",
+  "editType": "edit",
+  "executionStartTime": "17:14:00",
+  "executionEndTime": "17:13:59",
+  "corOrgNum": "55150921170238687000"
+}</t>
+  </si>
+  <si>
+    <t>周界相机删除</t>
+  </si>
+  <si>
+    <t>/buswash/device/perimeter/camera/delete</t>
+  </si>
+  <si>
+    <t>周界相机状态修改</t>
+  </si>
+  <si>
+    <t>/buswash/device/perimeter/camera/enable</t>
+  </si>
+  <si>
+    <t>{
+  "enabled": 1,
+  "id": 240616
+}</t>
+  </si>
+  <si>
+    <t>周界相机查询</t>
+  </si>
+  <si>
+    <t>/buswash/device/perimeter/camera/search</t>
+  </si>
+  <si>
+    <t>{
+  "current": 1,
+  "orgNum": "",
+  "perSize": 2,
+  "siteId": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": [
+    {
+      "id": 240621,
+      "stationNum": "10000672",
+      "enabled": 1,
+      "executionStartTime": "05:16:00",
+      "executionEndTime": "20:16:59",
+      "deviceName": "江汉路站南",
+      "bindDeviceId": "be300344807c41b5aff9fd58297b95b6",
+      "siteId": 1,
+      "siteName": "阮家桥公交停车场",
+      "corOrgName": "一公司",
+      "createTime": "2024-10-08 09:16:43",
+      "heartTime": null,
+      "operatorName": "管理员"
+    },
+    {
+      "id": 270614,
+      "stationNum": "10000660",
+      "enabled": 1,
+      "executionStartTime": "17:13:00",
+      "executionEndTime": "16:40:59",
+      "deviceName": "小房间摄像头01-阮家桥-右",
+      "bindDeviceId": "c43263e75461453281599f9181084329",
+      "siteId": 1,
+      "siteName": "阮家桥公交停车场",
+      "corOrgName": "一公司",
+      "createTime": "2024-08-29 17:14:05",
+      "heartTime": "2024-09-14 10:43:07",
+      "operatorName": "管理员"
+    }
+  ],
+  "total": 7,
+  "success": true
+}</t>
+  </si>
+  <si>
     <t>设备管理模块/设备指令下发</t>
   </si>
   <si>
@@ -2423,28 +2536,32 @@
   <si>
     <t>{
   "adminPassword": "",
+  "alcoholModule": "",
+  "alcoholThreshold": 0,
+  "bodyTemperatureThreshold": 0,
+  "disinfectNumberOfPeople": 0,
+  "disinfectTime": 0,
   "faceOrgNum": "",
+  "infoCountDown": 5,
   "judgeType": [],
-  "loginType": [
-    1
-  ],
+  "loginType": [],
+  "name": "测试1",
   "searchType": [],
-  "name": "测试1",
-  "disinfectNumberOfPeople": 0,
-  "disinfectTime": 0
-}</t>
-  </si>
-  <si>
-    <t>{
-  "retcode": "40007",
-  "retmsg": "模板名称重复",
+  "title": "",
+  "windowCountDown": 2
+}</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "模版功能已停用",
   "data": null,
   "total": null,
-  "success": false
-}</t>
-  </si>
-  <si>
-    <t>"success":false</t>
+  "success": true
+}</t>
+  </si>
+  <si>
+    <t>"success":true</t>
   </si>
   <si>
     <t>删除签到机配置模板</t>
@@ -2656,34 +2773,11 @@
   <si>
     <t>{
   "current": 1,
-  "end_time": "",
+  "end_time": "2023-11-07 23:59:59",
   "per_size": 1,
-  "start_time": "",
-  "station_num": "",
-  "type": ""
-}</t>
-  </si>
-  <si>
-    <t>{
-  "retcode": "0",
-  "retmsg": "操作成功",
-  "data": [
-    {
-      "id": 2941,
-      "station_num": "10000294",
-      "message": "测试1",
-      "emp_job_id": "1",
-      "emp_name": "1",
-      "ic_card": "1",
-      "org_num": null,
-      "org_name": null,
-      "state": 1,
-      "create_time": "2023-09-27 10:36:22",
-      "update_time": "2023-09-27 10:36:22"
-    }
-  ],
-  "total": 978,
-  "success": true
+  "start_time": "2023-11-07 00:00:00",
+  "station_num": "1",
+  "type": "1"
 }</t>
   </si>
   <si>
@@ -3370,7 +3464,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -5950,7 +6044,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.4778761061947" customWidth="1"/>
@@ -6284,7 +6378,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" ht="94.5" spans="1:10">
+    <row r="11" ht="110" customHeight="1" spans="1:10">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6310,10 +6404,10 @@
         <v>200</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>253</v>
+        <v>15</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" ht="94.5" spans="1:10">
@@ -6321,429 +6415,429 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>258</v>
+        <v>112</v>
       </c>
       <c r="H12">
         <v>200</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>259</v>
+        <v>15</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="13" ht="67.5" spans="1:8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" ht="94.5" spans="1:10">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C13" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="H13">
         <v>200</v>
       </c>
-    </row>
-    <row r="14" ht="134" customHeight="1" spans="1:10">
+      <c r="I13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="167" customHeight="1" spans="1:10">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C14" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="H14">
         <v>200</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" ht="145" customHeight="1" spans="1:10">
+    <row r="15" ht="94.5" spans="1:10">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C15" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H15">
         <v>200</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" ht="128" customHeight="1" spans="1:10">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="16" ht="94.5" spans="1:10">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C16" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>270</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H16">
+        <v>200</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="J16" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="H16">
-        <v>200</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" ht="142" customHeight="1" spans="1:10">
+    </row>
+    <row r="17" ht="67.5" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="C17" t="s">
         <v>275</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
         <v>276</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>277</v>
+        <v>14</v>
       </c>
       <c r="H17">
         <v>200</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" ht="94.5" spans="1:10">
+    </row>
+    <row r="18" ht="134" customHeight="1" spans="1:10">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="C18" t="s">
+        <v>277</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
         <v>278</v>
       </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H18">
         <v>200</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="19" ht="165" customHeight="1" spans="1:10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="145" customHeight="1" spans="1:10">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="C19" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="H19">
         <v>200</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" ht="94.5" spans="1:10">
+    <row r="20" ht="128" customHeight="1" spans="1:10">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="C20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H20">
         <v>200</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>286</v>
+        <v>15</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21" ht="150" customHeight="1" spans="1:10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="142" customHeight="1" spans="1:10">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" t="s">
         <v>288</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
         <v>289</v>
       </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>291</v>
-      </c>
       <c r="H21">
         <v>200</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>292</v>
+        <v>220</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" ht="108" spans="1:10">
+    <row r="22" ht="94.5" spans="1:10">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>295</v>
+        <v>14</v>
       </c>
       <c r="H22">
         <v>200</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="23" ht="94.5" spans="1:10">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" ht="165" customHeight="1" spans="1:10">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="C23" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>301</v>
+        <v>14</v>
       </c>
       <c r="H23">
         <v>200</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="24" ht="146" customHeight="1" spans="1:10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" ht="94.5" spans="1:10">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C24" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="H24">
         <v>200</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>15</v>
+        <v>299</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" ht="94.5" spans="1:10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" ht="150" customHeight="1" spans="1:10">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>236</v>
+        <v>301</v>
       </c>
       <c r="C25" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="H25">
         <v>200</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>16</v>
@@ -6754,86 +6848,86 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="C26" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="H26">
         <v>200</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="27" ht="108" spans="1:10">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="27" ht="94.5" spans="1:10">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C27" t="s">
+        <v>312</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>313</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="H27">
+        <v>200</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C27" t="s">
-        <v>317</v>
-      </c>
-      <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" t="s">
-        <v>318</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H27">
-        <v>200</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="28" ht="145" customHeight="1" spans="1:10">
+    </row>
+    <row r="28" ht="146" customHeight="1" spans="1:10">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C28" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="H28">
         <v>200</v>
@@ -6850,22 +6944,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>326</v>
+        <v>236</v>
       </c>
       <c r="C29" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="H29">
         <v>200</v>
@@ -6877,131 +6971,140 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" ht="154" customHeight="1" spans="1:10">
+    <row r="30" ht="108" spans="1:10">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>322</v>
+        <v>236</v>
       </c>
       <c r="C30" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="H30">
         <v>200</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="31" ht="94.5" spans="1:10">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" ht="108" spans="1:10">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C31" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="H31">
         <v>200</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>15</v>
+        <v>333</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" ht="54" spans="1:10">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="32" ht="145" customHeight="1" spans="1:10">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="C32" t="s">
+        <v>336</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>337</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" t="s">
-        <v>339</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="H32">
         <v>200</v>
       </c>
-      <c r="I32" t="s">
-        <v>245</v>
+      <c r="I32" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" ht="54" spans="1:8">
+    <row r="33" ht="94.5" spans="1:10">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C33" t="s">
         <v>340</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
         <v>341</v>
       </c>
-      <c r="D33" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="H33">
         <v>200</v>
       </c>
-    </row>
-    <row r="34" ht="54" spans="1:9">
+      <c r="I33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" ht="154" customHeight="1" spans="1:10">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C34" t="s">
         <v>343</v>
@@ -7016,45 +7119,48 @@
         <v>20</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>112</v>
+        <v>345</v>
       </c>
       <c r="H34">
         <v>200</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="35" ht="121.5" spans="1:10">
+        <v>346</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="35" ht="94.5" spans="1:10">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C35" t="s">
+        <v>348</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>349</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="H35">
+        <v>200</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="J35" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H35">
-        <v>200</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="36" ht="94.5" spans="1:10">
@@ -7062,92 +7168,83 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="C36" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H36">
         <v>200</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" ht="108" spans="1:10">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37" ht="54" spans="1:8">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C37" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>355</v>
+        <v>112</v>
       </c>
       <c r="H37">
         <v>200</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="38" ht="94.5" spans="1:10">
+    </row>
+    <row r="38" ht="54" spans="1:9">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C38" t="s">
+        <v>356</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
+        <v>357</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H38">
+        <v>200</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="D38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" t="s">
-        <v>359</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="H38">
-        <v>200</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="39" ht="121.5" spans="1:10">
@@ -7155,51 +7252,51 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C39" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="H39">
         <v>200</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="40" ht="148.5" spans="1:10">
+    <row r="40" ht="94.5" spans="1:10">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="C40" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>370</v>
+        <v>14</v>
       </c>
       <c r="H40">
         <v>200</v>
@@ -7211,67 +7308,192 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" ht="159" customHeight="1" spans="1:10">
+    <row r="41" ht="108" spans="1:10">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C41" t="s">
+        <v>366</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
         <v>367</v>
       </c>
-      <c r="C41" t="s">
-        <v>371</v>
-      </c>
-      <c r="D41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" t="s">
-        <v>372</v>
-      </c>
       <c r="F41" s="3" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="H41">
         <v>200</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" ht="154" customHeight="1" spans="1:10">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" ht="94.5" spans="1:10">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C42" t="s">
+        <v>371</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>372</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H42">
+        <v>200</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="J42" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" t="s">
+    </row>
+    <row r="43" ht="121.5" spans="1:10">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="3" t="s">
+      <c r="C43" t="s">
         <v>377</v>
       </c>
-      <c r="H42">
-        <v>200</v>
-      </c>
-      <c r="I42" s="3" t="s">
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
         <v>378</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="F43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43">
+        <v>200</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" ht="148.5" spans="1:10">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C44" t="s">
+        <v>381</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>382</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H44">
+        <v>200</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" ht="159" customHeight="1" spans="1:10">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C45" t="s">
+        <v>384</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>385</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="H45">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" ht="154" customHeight="1" spans="1:10">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C46" t="s">
+        <v>388</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>389</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="H46">
+        <v>200</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7339,28 +7561,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="H2">
         <v>200</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>16</v>
@@ -7372,22 +7594,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="C3" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="H3">
         <v>200</v>
@@ -7404,22 +7626,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="C4" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="H4">
         <v>200</v>
@@ -7436,16 +7658,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="C5" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>14</v>
@@ -7454,7 +7676,7 @@
         <v>200</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>16</v>
@@ -7465,16 +7687,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="C6" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>14</v>
@@ -7483,7 +7705,7 @@
         <v>200</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>16</v>
@@ -7494,28 +7716,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C7" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="H7">
         <v>200</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>16</v>
@@ -7526,28 +7748,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="C8" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="H8">
         <v>200</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="J8" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" ht="135" spans="1:8">
@@ -7555,22 +7777,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C9" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="H9">
         <v>200</v>
@@ -7581,28 +7803,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C10" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="H10">
         <v>200</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>16</v>
@@ -7613,28 +7835,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C11" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="H11">
         <v>200</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>16</v>
@@ -7645,28 +7867,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C12" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="H12">
         <v>200</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>16</v>
@@ -7677,28 +7899,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C13" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="H13">
         <v>200</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>16</v>
@@ -7709,16 +7931,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C14" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>14</v>
@@ -7736,22 +7958,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C15" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="H15">
         <v>200</v>
@@ -7762,28 +7984,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C16" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="H16">
         <v>200</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>16</v>
@@ -7794,22 +8016,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C17" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="H17">
         <v>200</v>
@@ -7826,31 +8048,31 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C18" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="H18">
         <v>200</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="J18" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="19" ht="94.5" spans="1:10">
@@ -7858,31 +8080,31 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C19" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="H19">
         <v>200</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="J19" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" ht="121.5" spans="1:10">
@@ -7890,22 +8112,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C20" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="H20">
         <v>200</v>
@@ -7922,28 +8144,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C21" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="H21">
         <v>200</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>16</v>
